--- a/poc/fixtures/feature-rich.xlsx
+++ b/poc/fixtures/feature-rich.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R2a18778407f14a0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Data" sheetId="2" r:id="R5694091e3b5f4d56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R427d424983e949d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Data" sheetId="2" r:id="R1dc9565293c14c76"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -296,7 +296,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf91c3dc26bba4516"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R081a5ec12e7f4efc"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -651,7 +651,7 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="16" t="str">
-        <x:v>EVO_EDIT_MARKER_XLSX</x:v>
+        <x:v>CAPY_EDIT_MARKER_XLSX</x:v>
       </x:c>
       <x:c r="B9" s="16"/>
       <x:c r="C9" s="16"/>
@@ -680,7 +680,7 @@
     <x:mergeCell ref="A9:D9"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re33b36faaa994ac4"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35ee5edae6ba400e"/>
 </x:worksheet>
 </file>
 
